--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486489_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486489_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5618</v>
+        <v>5.6851</v>
       </c>
       <c r="E2" t="n">
         <v>3.335</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2268</v>
+        <v>2.3501</v>
       </c>
       <c r="G2" t="n">
         <v>3.6814</v>
@@ -610,13 +610,13 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3802</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>0.7126</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3324</v>
+        <v>-0.2091</v>
       </c>
       <c r="V2" t="n">
         <v>0.1952</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4909</v>
+        <v>5.3667</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7844</v>
+        <v>4.6294</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7066</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>3.9098</v>
@@ -688,13 +688,13 @@
         <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4061</v>
+        <v>1.2819</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3327</v>
+        <v>1.1777</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.1042</v>
       </c>
       <c r="V3" t="n">
         <v>-1.13</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.689</v>
+        <v>2.7836</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8221000000000001</v>
+        <v>1.0708</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8669</v>
+        <v>1.7128</v>
       </c>
       <c r="G4" t="n">
         <v>1.2705</v>
@@ -766,13 +766,13 @@
         <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3189</v>
+        <v>-1.2242</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6609</v>
+        <v>-0.4122</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6579</v>
+        <v>-0.8121</v>
       </c>
       <c r="V4" t="n">
         <v>3.3899</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0621</v>
+        <v>1.5795</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5631</v>
+        <v>1.2964</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4989</v>
+        <v>0.2832</v>
       </c>
       <c r="G5" t="n">
         <v>0.4741</v>
@@ -844,13 +844,13 @@
         <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0002</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8292</v>
+        <v>0.5624</v>
       </c>
       <c r="U5" t="n">
-        <v>0.171</v>
+        <v>-0.0448</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9347</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3405</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3628</v>
+        <v>-0.0158</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9777</v>
+        <v>0.6695</v>
       </c>
       <c r="G6" t="n">
         <v>0.9089</v>
@@ -922,13 +922,13 @@
         <v>0.6525</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1694</v>
+        <v>-0.5173</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1406</v>
+        <v>-0.2379</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0288</v>
+        <v>-0.2794</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3904</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. NASPLER PERAIRE</t>
+          <t>J. ROUND</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0356</v>
+        <v>-0.2079</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1081</v>
+        <v>-1.7811</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0725</v>
+        <v>1.5732</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7702</v>
+        <v>1.7104</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5814</v>
+        <v>1.4323</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1889</v>
+        <v>0.2781</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.9765</v>
+        <v>0.2587</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.9765</v>
+        <v>1.0037</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.7451</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2063</v>
+        <v>1.4518</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3951</v>
+        <v>0.4286</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1889</v>
+        <v>1.0231</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7999000000000001</v>
+        <v>-0.7661</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7607</v>
+        <v>-0.2127</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0392</v>
+        <v>-0.5534</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9347</v>
+        <v>-0.9347</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1952</v>
+        <v>-0.7395</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7395</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. KRISTENSEN</t>
+          <t>C. ROGERS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.295</v>
+        <v>-0.2805</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.914</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.619</v>
+        <v>-0.2114</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.146</v>
+        <v>1.3691</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.146</v>
+        <v>1.2017</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.1673</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7086</v>
+        <v>0.2193</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0365</v>
+        <v>-0.2214</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7451</v>
+        <v>0.4407</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5626</v>
+        <v>1.1498</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1825</v>
+        <v>1.4231</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7451</v>
+        <v>-0.2733</v>
       </c>
       <c r="P8" t="n">
-        <v>0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.584</v>
+        <v>0.2629</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2055</v>
+        <v>0.7991</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3785</v>
+        <v>-0.5363</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. LO</t>
+          <t>D. KRISTENSEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.455</v>
+        <v>-0.295</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7083</v>
+        <v>-0.914</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2533</v>
+        <v>0.619</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1908</v>
+        <v>-0.146</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2316</v>
+        <v>-0.146</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4224</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3725</v>
+        <v>-0.7086</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.4108</v>
+        <v>0.0365</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0382</v>
+        <v>-0.7451</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5633</v>
+        <v>0.5626</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1792</v>
+        <v>-0.1825</v>
       </c>
       <c r="O9" t="n">
-        <v>2.3842</v>
+        <v>0.7451</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9079</v>
+        <v>-0.584</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4434</v>
+        <v>-0.2055</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4645</v>
+        <v>-0.3785</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. ROUND</t>
+          <t>O. LO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7966</v>
+        <v>-0.3171</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1849</v>
+        <v>-2.4162</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3882</v>
+        <v>2.0991</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7104</v>
+        <v>1.1908</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4323</v>
+        <v>-1.2316</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2781</v>
+        <v>2.4224</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2587</v>
+        <v>-1.3725</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0037</v>
+        <v>-1.4108</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7451</v>
+        <v>0.0382</v>
       </c>
       <c r="M10" t="n">
-        <v>1.4518</v>
+        <v>2.5633</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4286</v>
+        <v>0.1792</v>
       </c>
       <c r="O10" t="n">
-        <v>1.0231</v>
+        <v>2.3842</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2175</v>
+        <v>0.2175</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3548</v>
+        <v>-0.77</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6165</v>
+        <v>-0.1514</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7383</v>
+        <v>-0.6186</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9347</v>
+        <v>-0.9554</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7395</v>
+        <v>0.1952</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1952</v>
+        <v>-1.1507</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. ROGERS</t>
+          <t>T. NASPLER PERAIRE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8499</v>
+        <v>-0.9845</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3611</v>
+        <v>-2.9337</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4888</v>
+        <v>1.9492</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3691</v>
+        <v>-1.7702</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2017</v>
+        <v>-1.5814</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1673</v>
+        <v>-0.1889</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2193</v>
+        <v>-1.9765</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2214</v>
+        <v>-1.9765</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4407</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1498</v>
+        <v>0.2063</v>
       </c>
       <c r="N11" t="n">
-        <v>1.4231</v>
+        <v>0.3951</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2733</v>
+        <v>-0.1889</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R11" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3066</v>
+        <v>-0.149</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5071</v>
+        <v>-0.0649</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8137</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.695</v>
+        <v>0.9347</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.695</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0416</v>
+        <v>-1.7688</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5689</v>
+        <v>-2.3886</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5273</v>
+        <v>0.6198</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5566</v>
@@ -1390,13 +1390,13 @@
         <v>0.6525</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0499</v>
+        <v>-0.7772</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4675</v>
+        <v>-0.2872</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5825</v>
+        <v>-0.49</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.2937</v>
+        <v>-3.153</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.7202</v>
+        <v>-3.8261</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4265</v>
+        <v>0.6731</v>
       </c>
       <c r="G13" t="n">
         <v>-1.1442</v>
@@ -1468,13 +1468,13 @@
         <v>1.5225</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6492</v>
+        <v>0.4915</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3629</v>
+        <v>0.5312</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2863</v>
+        <v>-0.0397</v>
       </c>
       <c r="V13" t="n">
         <v>-0.7602</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.376899999999999</v>
+        <v>9.061799999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.6981</v>
+        <v>-4.013</v>
       </c>
       <c r="F14" t="n">
-        <v>13.0749</v>
+        <v>13.075</v>
       </c>
       <c r="G14" t="n">
         <v>10.898</v>
@@ -1519,10 +1519,10 @@
         <v>-3.7016</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1053000000000002</v>
+        <v>-0.1052999999999997</v>
       </c>
       <c r="K14" t="n">
-        <v>8.4129</v>
+        <v>8.412900000000002</v>
       </c>
       <c r="L14" t="n">
         <v>-8.5185</v>
@@ -1546,13 +1546,13 @@
         <v>13.05</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.4155</v>
+        <v>-1.7304</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5262</v>
+        <v>2.211199999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.9417</v>
+        <v>-3.9418</v>
       </c>
       <c r="V14" t="n">
         <v>-2.2806</v>
@@ -1561,7 +1561,7 @@
         <v>4.756399999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.037199999999999</v>
+        <v>-7.0372</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.851</v>
+        <v>2.4721</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3504</v>
+        <v>2.7916</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4993</v>
+        <v>-0.3195</v>
       </c>
       <c r="G15" t="n">
         <v>0.9467</v>
@@ -1624,13 +1624,13 @@
         <v>0.2175</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9266</v>
+        <v>0.5477</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9421</v>
+        <v>0.3833</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0155</v>
+        <v>0.1643</v>
       </c>
       <c r="V15" t="n">
         <v>0.7602</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1601</v>
+        <v>2.3142</v>
       </c>
       <c r="E16" t="n">
         <v>2.3521</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.192</v>
+        <v>-0.0379</v>
       </c>
       <c r="G16" t="n">
         <v>-0.3953</v>
@@ -1702,13 +1702,13 @@
         <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2504</v>
+        <v>1.4045</v>
       </c>
       <c r="T16" t="n">
         <v>0.9661999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2842</v>
+        <v>0.4383</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. VICEDO AYALA</t>
+          <t>S. LITTLESON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4022</v>
+        <v>0.8386</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1226</v>
+        <v>0.0549</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5249</v>
+        <v>0.7837</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3921</v>
+        <v>1.1043</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4479</v>
+        <v>-1.174</v>
       </c>
       <c r="I17" t="n">
-        <v>1.84</v>
+        <v>2.2783</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2803</v>
+        <v>1.3293</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.1616</v>
+        <v>0.1587</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8813</v>
+        <v>1.1706</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6723</v>
+        <v>-0.225</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2863</v>
+        <v>-1.3327</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9586</v>
+        <v>1.1076</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6525</v>
+        <v>-1.305</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2175</v>
+        <v>-3.2626</v>
       </c>
       <c r="R17" t="n">
-        <v>0.87</v>
+        <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4472</v>
+        <v>0.2998</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6249</v>
+        <v>0.2932</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1777</v>
+        <v>0.0066</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1952</v>
+        <v>0.7395</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1952</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. WEMBI</t>
+          <t>E. VICEDO AYALA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1903</v>
+        <v>0.8353</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9433</v>
+        <v>-0.7874</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1336</v>
+        <v>1.6226</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5775</v>
+        <v>0.3921</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.9593</v>
+        <v>-1.4479</v>
       </c>
       <c r="I18" t="n">
-        <v>2.3818</v>
+        <v>1.84</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8052</v>
+        <v>-0.2803</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.1439</v>
+        <v>-1.1616</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3387</v>
+        <v>0.8813</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2277</v>
+        <v>0.6723</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8153</v>
+        <v>-0.2863</v>
       </c>
       <c r="O18" t="n">
-        <v>1.0431</v>
+        <v>0.9586</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1751</v>
+        <v>-0.2175</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>2.3996</v>
+        <v>-0.0141</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5813</v>
+        <v>-0.2896</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1817</v>
+        <v>0.2755</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5443</v>
+        <v>-0.1952</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.5443</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4711</v>
+        <v>-0.4595</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2814</v>
+        <v>-1.3932</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8103</v>
+        <v>0.9336</v>
       </c>
       <c r="G19" t="n">
         <v>-1.2158</v>
@@ -1936,13 +1936,13 @@
         <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2673</v>
+        <v>0.2788</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2656</v>
+        <v>0.1538</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0017</v>
+        <v>0.125</v>
       </c>
       <c r="V19" t="n">
         <v>1.13</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SOLA IDDRISU</t>
+          <t>F. SCHOTT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5998</v>
+        <v>-0.863</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4853</v>
+        <v>-0.9197</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8856</v>
+        <v>0.0567</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.0802</v>
+        <v>-0.6823</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5813</v>
+        <v>-1.2441</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.4989</v>
+        <v>0.5618</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.8886</v>
+        <v>-0.6121</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5689</v>
+        <v>-0.7268</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.4575</v>
+        <v>0.1147</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1916</v>
+        <v>-0.0703</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1502</v>
+        <v>-0.5173</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9586</v>
+        <v>0.447</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>3.0024</v>
+        <v>0.2968</v>
       </c>
       <c r="T20" t="n">
-        <v>2.4479</v>
+        <v>-0.0901</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5546</v>
+        <v>0.3869</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7395</v>
+        <v>-1.13</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. LITTLESON</t>
+          <t>J. LOBO MARTORELL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7131999999999999</v>
+        <v>-1.1053</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8391999999999999</v>
+        <v>-1.9135</v>
       </c>
       <c r="F21" t="n">
-        <v>0.126</v>
+        <v>0.8082</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1043</v>
+        <v>-3.2413</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.174</v>
+        <v>-2.9593</v>
       </c>
       <c r="I21" t="n">
-        <v>2.2783</v>
+        <v>-0.2821</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3293</v>
+        <v>-3.7671</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1587</v>
+        <v>-2.1439</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1706</v>
+        <v>-1.6232</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.225</v>
+        <v>0.5258</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3327</v>
+        <v>-0.8153</v>
       </c>
       <c r="O21" t="n">
-        <v>1.1076</v>
+        <v>1.3411</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9576</v>
+        <v>0.435</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2519</v>
+        <v>0.2013</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6008</v>
+        <v>0.1586</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6511</v>
+        <v>0.0427</v>
       </c>
       <c r="V21" t="n">
-        <v>0.7395</v>
+        <v>1.4997</v>
       </c>
       <c r="W21" t="n">
         <v>1.695</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.9554</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. SCHOTT</t>
+          <t>E. WEMBI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4218</v>
+        <v>-1.1752</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0314</v>
+        <v>-2.3962</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3903</v>
+        <v>1.2209</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6823</v>
+        <v>-0.5775</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2441</v>
+        <v>-2.9593</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5618</v>
+        <v>2.3818</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6121</v>
+        <v>-0.8052</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7268</v>
+        <v>-2.1439</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1147</v>
+        <v>1.3387</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0703</v>
+        <v>0.2277</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5173</v>
+        <v>-0.8153</v>
       </c>
       <c r="O22" t="n">
-        <v>0.447</v>
+        <v>1.0431</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6525</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2175</v>
+        <v>-2.1751</v>
       </c>
       <c r="R22" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.262</v>
+        <v>1.0341</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2019</v>
+        <v>1.1284</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0601</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.13</v>
+        <v>-0.5443</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.5443</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. LOBO MARTORELL</t>
+          <t>A. SOLA IDDRISU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.485</v>
+        <v>-1.6479</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0311</v>
+        <v>-3.8264</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5461</v>
+        <v>2.1785</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.2413</v>
+        <v>-3.0802</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.9593</v>
+        <v>-0.5813</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2821</v>
+        <v>-2.4989</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.7671</v>
+        <v>-2.8886</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.1439</v>
+        <v>0.5689</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.6232</v>
+        <v>-3.4575</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5258</v>
+        <v>-0.1916</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8153</v>
+        <v>-1.1502</v>
       </c>
       <c r="O23" t="n">
-        <v>1.3411</v>
+        <v>0.9586</v>
       </c>
       <c r="P23" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R23" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1784</v>
+        <v>1.9543</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9589</v>
+        <v>1.1068</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2194</v>
+        <v>0.8475</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4997</v>
+        <v>-0.7395</v>
       </c>
       <c r="W23" t="n">
-        <v>1.695</v>
+        <v>-0.7395</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0161</v>
+        <v>-1.9147</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.7357</v>
+        <v>-2.8417</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2804</v>
+        <v>0.927</v>
       </c>
       <c r="G24" t="n">
         <v>-2.6613</v>
@@ -2326,13 +2326,13 @@
         <v>1.5225</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6577</v>
+        <v>0.4437</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3953</v>
+        <v>0.4987</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.2624</v>
+        <v>-0.055</v>
       </c>
       <c r="V24" t="n">
         <v>0.9554</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.2737</v>
+        <v>-3.9462</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.3074</v>
+        <v>-4.1957</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0337</v>
+        <v>0.2495</v>
       </c>
       <c r="G25" t="n">
         <v>-1.4872</v>
@@ -2404,13 +2404,13 @@
         <v>0.435</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6337</v>
+        <v>-0.3061</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4795</v>
+        <v>-0.3677</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1542</v>
+        <v>0.0616</v>
       </c>
       <c r="V25" t="n">
         <v>-0.1952</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.377099999999999</v>
+        <v>-4.651599999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-13.0749</v>
+        <v>-13.0752</v>
       </c>
       <c r="F26" t="n">
-        <v>4.698199999999999</v>
+        <v>8.423299999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-10.8978</v>
@@ -2452,7 +2452,7 @@
         <v>-14.5996</v>
       </c>
       <c r="I26" t="n">
-        <v>3.7016</v>
+        <v>3.701600000000001</v>
       </c>
       <c r="J26" t="n">
         <v>-11.0035</v>
@@ -2470,7 +2470,7 @@
         <v>-8.412799999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>8.5183</v>
+        <v>8.518299999999998</v>
       </c>
       <c r="P26" t="n">
         <v>-2.1751</v>
@@ -2482,22 +2482,22 @@
         <v>10.8751</v>
       </c>
       <c r="S26" t="n">
-        <v>2.415400000000001</v>
+        <v>6.1408</v>
       </c>
       <c r="T26" t="n">
-        <v>3.941800000000001</v>
+        <v>3.9416</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.5262</v>
+        <v>2.1991</v>
       </c>
       <c r="V26" t="n">
         <v>2.2806</v>
       </c>
       <c r="W26" t="n">
-        <v>7.037199999999999</v>
+        <v>7.0372</v>
       </c>
       <c r="X26" t="n">
-        <v>-4.756499999999999</v>
+        <v>-4.7565</v>
       </c>
     </row>
   </sheetData>
